--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_LIVERSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε._(168)_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_LIVERSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε._(168)_2026-02.xlsx
@@ -1,1565 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="620" yWindow="780" windowWidth="29400" windowHeight="17220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energy Production" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Energy Production'!$B$1:$H$57</definedName>
-  </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="[$€-2]\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="[$€-2]\ 0.00"/>
-    <numFmt numFmtId="168" formatCode="#.##&quot; &quot;[$€-2]&quot;/MWh&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-  </numFmts>
-  <fonts count="23">
-    <font>
-      <name val="Avenir Next Regular"/>
-      <color indexed="8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <color indexed="8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <color indexed="8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <color indexed="10"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color indexed="10"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <color indexed="8"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color indexed="8"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <color indexed="8"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <i val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <i val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <color indexed="8"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <b val="1"/>
-      <sz val="20"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Century Gothic"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-  </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="39">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </left>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </right>
-      <top style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="6" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="113">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="26"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="15"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="26"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="15"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="26"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="15"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="24"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="24"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="24"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="24"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="24"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="24"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="27"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="27"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="27"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="11"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="24"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="24"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="11"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="24"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="24"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="11"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="24"/>
-        </left>
-        <right style="thin">
-          <color indexed="24"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="24"/>
-        </vertical>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="15"/>
-        </right>
-        <top style="thin">
-          <color indexed="14"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="14"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="15"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="15"/>
-        </right>
-        <top style="thin">
-          <color indexed="14"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="14"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="15"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="14"/>
-        </right>
-        <top style="thin">
-          <color indexed="24"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="15"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="25"/>
-          <bgColor indexed="23"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="14"/>
-        </right>
-        <top style="thin">
-          <color indexed="14"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="24"/>
-        </bottom>
-        <horizontal style="thin">
-          <color indexed="15"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color indexed="14"/>
-        </left>
-        <right style="thin">
-          <color indexed="14"/>
-        </right>
-        <top style="thin">
-          <color indexed="14"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="14"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="15"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="15"/>
-        </horizontal>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="PivotStyleCustom01" count="17">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstSubtotalColumn" dxfId="11"/>
-      <tableStyleElement type="secondSubtotalColumn" dxfId="10"/>
-      <tableStyleElement type="thirdSubtotalColumn" dxfId="9"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="8"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="7"/>
-      <tableStyleElement type="thirdSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumnSubheading" dxfId="5"/>
-      <tableStyleElement type="secondColumnSubheading" dxfId="4"/>
-      <tableStyleElement type="thirdColumnSubheading" dxfId="3"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="2"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="1"/>
-      <tableStyleElement type="thirdRowSubheading" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFBEF"/>
-      <rgbColor rgb="FF5C5C5C"/>
-      <rgbColor rgb="FFF0EBE2"/>
-      <rgbColor rgb="FFFEFFFE"/>
-      <rgbColor rgb="FF5A5754"/>
-      <rgbColor rgb="FFB3AFAA"/>
-      <rgbColor rgb="FFCCCAC6"/>
-      <rgbColor rgb="FFE4E2DE"/>
-      <rgbColor rgb="FFD1D2D4"/>
-      <rgbColor rgb="FFE0E1E2"/>
-      <rgbColor rgb="FFB8B8B8"/>
-      <rgbColor rgb="FFE4E2E0"/>
-      <rgbColor rgb="FF55A86E"/>
-      <rgbColor rgb="FF494A49"/>
-      <rgbColor rgb="FFE6E2DF"/>
-      <rgbColor rgb="FF9A958E"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="FFF4F0E5"/>
-      <rgbColor rgb="FFDFDAD2"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
@@ -2845,7 +1283,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3197,13 +1635,13 @@
         <v>2600.01</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0</v>
+        <v>66.4089699</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>2.6</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>0</v>
+        <v>25.54</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3237,13 +1675,13 @@
         <v>4526.64</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0</v>
+        <v>44.5169463</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>4.53</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>0</v>
+        <v>9.83</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3417,13 +1855,13 @@
         <v>6355.8</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>26.568639</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>6.36</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3437,13 +1875,13 @@
         <v>6279.75</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>36.6726045</v>
+        <v>29.7445026</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>6.28</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>5.84</v>
+        <v>4.74</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3457,13 +1895,13 @@
         <v>6183.39</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0</v>
+        <v>96.5004663</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>6.18</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>0</v>
+        <v>15.61</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3477,13 +1915,13 @@
         <v>4486.26</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>13.1327022</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>4.49</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3497,13 +1935,13 @@
         <v>95393.52</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>2457.92</v>
+        <v>2698.12</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>95.42</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>25.77</v>
+        <v>28.28</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3602,7 +2040,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>2457.92</v>
+        <v>2698.12</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3707,7 +2145,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
